--- a/03_Prompting/outputs/GPT/RESULT_pan_gpt-4o_persona_zeroshot_cot.xlsx
+++ b/03_Prompting/outputs/GPT/RESULT_pan_gpt-4o_persona_zeroshot_cot.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1785,7 +1785,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1819,7 +1819,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2057,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2210,7 +2210,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2737,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4386,7 +4386,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4420,7 +4420,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -5457,7 +5457,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -5831,7 +5831,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6273,7 +6273,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -6647,7 +6647,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7582,7 +7582,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -8194,7 +8194,7 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8619,7 +8619,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -8942,7 +8942,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -9911,7 +9911,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -10999,7 +10999,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -11934,7 +11934,7 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -12325,7 +12325,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12410,7 +12410,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12461,7 +12461,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12529,7 +12529,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12750,7 +12750,7 @@
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -12835,7 +12835,7 @@
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -13362,7 +13362,7 @@
       </c>
       <c r="C761" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -13651,7 +13651,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -13991,7 +13991,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -14365,7 +14365,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -14654,7 +14654,7 @@
       </c>
       <c r="C837" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15147,7 +15147,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15164,7 +15164,7 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15572,7 +15572,7 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15623,7 +15623,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15674,7 +15674,7 @@
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15827,7 @@
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -15844,7 +15844,7 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -16048,7 +16048,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -16354,7 +16354,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -16405,7 +16405,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -16422,7 +16422,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -16592,7 +16592,7 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="C956" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -16881,7 +16881,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -17442,7 +17442,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -17459,7 +17459,7 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -17595,7 +17595,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -17731,7 +17731,7 @@
       </c>
       <c r="C1018" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -18530,7 +18530,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -19023,7 +19023,7 @@
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -19040,7 +19040,7 @@
       </c>
       <c r="C1095" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -19346,7 +19346,7 @@
       </c>
       <c r="C1113" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -19431,7 +19431,7 @@
       </c>
       <c r="C1118" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -19720,7 +19720,7 @@
       </c>
       <c r="C1135" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -19992,7 +19992,7 @@
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -20111,7 +20111,7 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -20230,7 +20230,7 @@
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -20502,7 +20502,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
       </c>
       <c r="C1191" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -20723,7 +20723,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -20859,7 +20859,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21182,7 +21182,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -21233,7 +21233,7 @@
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -21301,7 +21301,7 @@
       </c>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21352,7 +21352,7 @@
       </c>
       <c r="C1231" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21505,7 +21505,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -21743,7 +21743,7 @@
       </c>
       <c r="C1254" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -21845,7 +21845,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -22151,7 +22151,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -22236,7 +22236,7 @@
       </c>
       <c r="C1283" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information giving</t>
         </is>
       </c>
     </row>
@@ -22525,7 +22525,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>problem discovery</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -23035,7 +23035,7 @@
       </c>
       <c r="C1330" t="inlineStr">
         <is>
-          <t>feature request</t>
+          <t>information seeking</t>
         </is>
       </c>
     </row>
@@ -23256,7 +23256,7 @@
       </c>
       <c r="C1343" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>feature request</t>
         </is>
       </c>
     </row>
@@ -23477,7 +23477,7 @@
       </c>
       <c r="C1356" t="inlineStr">
         <is>
-          <t>information seeking</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -23732,7 +23732,7 @@
       </c>
       <c r="C1371" t="inlineStr">
         <is>
-          <t>information giving</t>
+          <t>problem discovery</t>
         </is>
       </c>
     </row>
@@ -24109,7 +24109,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7784172661870503</v>
+        <v>0.7669064748201438</v>
       </c>
     </row>
     <row r="3">
@@ -24119,7 +24119,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7053021286755006</v>
+        <v>0.6846592087686438</v>
       </c>
     </row>
     <row r="4">
@@ -24129,7 +24129,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7780988912933827</v>
+        <v>0.7608355003420527</v>
       </c>
     </row>
     <row r="5">
@@ -24139,7 +24139,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7441730239008011</v>
+        <v>0.7559751299055462</v>
       </c>
     </row>
     <row r="6">
@@ -24149,7 +24149,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.711856651129416</v>
+        <v>0.6900459319424677</v>
       </c>
     </row>
     <row r="7">
@@ -24159,7 +24159,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>419.6855573459998</v>
+        <v>766.5928407320171</v>
       </c>
     </row>
     <row r="8">
@@ -24169,7 +24169,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3019320556446041</v>
+        <v>0.5515056408144008</v>
       </c>
     </row>
   </sheetData>
